--- a/Lab_4/data/partB/param_optimization_process/v150_k40_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k40_s200_results.xlsx
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
         <v>1</v>
@@ -530,7 +530,7 @@
         <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
         <v>5</v>
@@ -539,19 +539,19 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="N2" t="n">
         <v>4</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -573,16 +573,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -594,22 +594,22 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -677,40 +677,40 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -738,19 +738,19 @@
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
@@ -759,16 +759,16 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7">
@@ -790,13 +790,13 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
@@ -811,16 +811,16 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="N7" t="n">
+        <v>8</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>10</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -833,7 +833,7 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -848,31 +848,31 @@
         <v>13</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
         <v>2</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -882,31 +882,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
         <v>1</v>
       </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
+        <v>53</v>
+      </c>
+      <c r="J9" t="n">
         <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>54</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -918,13 +918,13 @@
         <v>12</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,16 +937,16 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -958,16 +958,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
         <v>2</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,28 +1059,28 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1090,49 +1090,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1142,22 +1142,22 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1166,25 +1166,25 @@
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1218,22 +1218,22 @@
         <v>5</v>
       </c>
       <c r="J15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,28 +1246,28 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" t="n">
         <v>1</v>
-      </c>
-      <c r="C16" t="n">
-        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
         <v>2</v>
@@ -1276,19 +1276,19 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
         <v>2</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
       <c r="P16" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4038,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6537,7 +6537,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9070,7 +9070,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12215,7 +12215,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12300,7 +12300,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12844,7 +12844,7 @@
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13813,7 +13813,7 @@
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14085,7 +14085,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15343,7 +15343,7 @@
       </c>
       <c r="C826" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18199,7 +18199,7 @@
       </c>
       <c r="C994" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="C1051" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20715,7 +20715,7 @@
       </c>
       <c r="C1142" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21854,7 +21854,7 @@
       </c>
       <c r="C1209" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22313,7 +22313,7 @@
       </c>
       <c r="C1236" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="C1258" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24098,7 +24098,7 @@
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24778,7 +24778,7 @@
       </c>
       <c r="C1381" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25203,7 +25203,7 @@
       </c>
       <c r="C1406" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
